--- a/jogos_2025-08-09.xlsx
+++ b/jogos_2025-08-09.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,22 +7370,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7502,22 +7502,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,22 +8030,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,22 +14498,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14846,10 +14846,10 @@
         <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD109" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,22 +17270,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="M130" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N130" t="n">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="M132" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N132" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC132" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18194,22 +18194,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,10 +18806,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC139" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD139" t="n">
         <v>0</v>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19070,10 +19070,10 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC141" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD141" t="n">
         <v>0</v>
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="M142" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="N142" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19202,10 +19202,10 @@
         <v>0</v>
       </c>
       <c r="AB142" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC142" t="n">
         <v>2.26</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>1.54</v>
       </c>
       <c r="AD142" t="n">
         <v>0</v>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19286,13 +19286,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19334,10 +19334,10 @@
         <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD143" t="n">
         <v>0</v>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19466,10 +19466,10 @@
         <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD144" t="n">
         <v>0</v>
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19682,13 +19682,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19730,10 +19730,10 @@
         <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD146" t="n">
         <v>0</v>
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L148" t="n">
@@ -20042,22 +20042,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20126,10 +20126,10 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC149" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD149" t="n">
         <v>0</v>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20210,13 +20210,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -20258,10 +20258,10 @@
         <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC150" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD150" t="n">
         <v>0</v>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="M153" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="N153" t="n">
-        <v>2.57</v>
+        <v>4.3</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20654,10 +20654,10 @@
         <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="AC153" t="n">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="AD153" t="n">
         <v>0</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20786,10 +20786,10 @@
         <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC154" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD154" t="n">
         <v>0</v>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20870,13 +20870,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20918,10 +20918,10 @@
         <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC155" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD155" t="n">
         <v>0</v>
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21314,10 +21314,10 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD158" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,10 +21710,10 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21842,10 +21842,10 @@
         <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD162" t="n">
         <v>0</v>
@@ -21890,22 +21890,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21974,10 +21974,10 @@
         <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD163" t="n">
         <v>0</v>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,22 +23078,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23342,22 +23342,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23606,22 +23606,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23870,7 +23870,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,22 +24002,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24398,22 +24398,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24662,22 +24662,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24694,17 +24694,17 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24740,10 +24740,10 @@
         <v>0</v>
       </c>
       <c r="Z184" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB184" t="n">
         <v>0</v>
@@ -24794,22 +24794,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24826,17 +24826,17 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24872,10 +24872,10 @@
         <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB185" t="n">
         <v>0</v>
@@ -24926,7 +24926,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25190,22 +25190,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25226,13 +25226,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AB188" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC188" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD188" t="n">
         <v>0</v>
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25358,13 +25358,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -25406,10 +25406,10 @@
         <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC189" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD189" t="n">
         <v>0</v>
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25754,13 +25754,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="M192" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N192" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25802,10 +25802,10 @@
         <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC192" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD192" t="n">
         <v>0</v>
@@ -25982,22 +25982,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26018,13 +26018,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="M194" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N194" t="n">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -26066,10 +26066,10 @@
         <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC194" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD194" t="n">
         <v>0</v>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC197" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC205" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27566,22 +27566,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27650,10 +27650,10 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -27698,22 +27698,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27830,22 +27830,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -28094,22 +28094,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC210" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28226,22 +28226,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28358,7 +28358,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28442,10 +28442,10 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC212" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD212" t="n">
         <v>0</v>
@@ -28490,22 +28490,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28764,12 +28764,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28790,13 +28790,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="M215" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N215" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28838,10 +28838,10 @@
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC215" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD215" t="n">
         <v>0</v>
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -29018,7 +29018,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29102,10 +29102,10 @@
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC217" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD217" t="n">
         <v>0</v>
@@ -29150,22 +29150,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29186,13 +29186,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -29234,10 +29234,10 @@
         <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC218" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD218" t="n">
         <v>0</v>
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29318,13 +29318,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -29366,10 +29366,10 @@
         <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD219" t="n">
         <v>0</v>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29450,13 +29450,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -29498,10 +29498,10 @@
         <v>0</v>
       </c>
       <c r="AB220" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD220" t="n">
         <v>0</v>
@@ -29546,22 +29546,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29762,10 +29762,10 @@
         <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
@@ -29810,7 +29810,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29820,12 +29820,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29846,13 +29846,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29894,10 +29894,10 @@
         <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC223" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD223" t="n">
         <v>0</v>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29952,12 +29952,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30374,13 +30374,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30602,22 +30602,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30734,7 +30734,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30744,12 +30744,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30770,13 +30770,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30812,10 +30812,10 @@
         <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB230" t="n">
         <v>0</v>
@@ -30866,22 +30866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30902,13 +30902,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30944,10 +30944,10 @@
         <v>0</v>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA231" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB231" t="n">
         <v>0</v>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -31008,12 +31008,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -31130,22 +31130,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -31262,7 +31262,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -31272,12 +31272,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -31298,13 +31298,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -31404,12 +31404,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -31536,12 +31536,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31562,13 +31562,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -31604,10 +31604,10 @@
         <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA236" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB236" t="n">
         <v>0</v>
@@ -31658,7 +31658,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -31668,12 +31668,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31790,22 +31790,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31868,10 +31868,10 @@
         <v>0</v>
       </c>
       <c r="Z238" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA238" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB238" t="n">
         <v>0</v>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31932,12 +31932,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -32054,7 +32054,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -32090,13 +32090,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -32196,12 +32196,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32450,22 +32450,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -32486,13 +32486,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -32540,10 +32540,10 @@
         <v>0</v>
       </c>
       <c r="AD243" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE243" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF243" t="n">
         <v>0</v>
@@ -32582,22 +32582,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -32672,10 +32672,10 @@
         <v>0</v>
       </c>
       <c r="AD244" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF244" t="n">
         <v>0</v>
@@ -32714,22 +32714,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32846,22 +32846,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -33252,12 +33252,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33648,12 +33648,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33780,12 +33780,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33912,12 +33912,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -34044,12 +34044,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -34176,12 +34176,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -34430,7 +34430,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -34440,12 +34440,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -34466,13 +34466,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -34514,10 +34514,10 @@
         <v>0</v>
       </c>
       <c r="AB258" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC258" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD258" t="n">
         <v>0</v>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -34572,12 +34572,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -34598,13 +34598,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -34646,10 +34646,10 @@
         <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC259" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD259" t="n">
         <v>0</v>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -34704,12 +34704,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34836,12 +34836,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34862,13 +34862,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="M261" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="N261" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34910,10 +34910,10 @@
         <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC261" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD261" t="n">
         <v>0</v>
@@ -34968,12 +34968,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34994,13 +34994,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.51</v>
+        <v>2.25</v>
       </c>
       <c r="M262" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="N262" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -35045,7 +35045,7 @@
         <v>2.3</v>
       </c>
       <c r="AC262" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD262" t="n">
         <v>0</v>
@@ -35090,7 +35090,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -35100,12 +35100,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -35222,7 +35222,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -35232,12 +35232,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -35354,7 +35354,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -35364,12 +35364,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -35496,12 +35496,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -35618,7 +35618,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -35628,12 +35628,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -35760,12 +35760,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35882,7 +35882,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35892,12 +35892,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -36014,7 +36014,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -36024,12 +36024,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -36146,7 +36146,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -36156,12 +36156,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -36278,7 +36278,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -36288,12 +36288,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -36552,12 +36552,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -36816,12 +36816,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36938,7 +36938,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36948,12 +36948,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -37070,7 +37070,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -37080,12 +37080,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -37466,7 +37466,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -37476,12 +37476,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -37502,13 +37502,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -37550,10 +37550,10 @@
         <v>0</v>
       </c>
       <c r="AB281" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC281" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD281" t="n">
         <v>0</v>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -37608,12 +37608,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -37634,13 +37634,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -37682,10 +37682,10 @@
         <v>0</v>
       </c>
       <c r="AB282" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC282" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD282" t="n">
         <v>0</v>
@@ -37740,12 +37740,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37766,13 +37766,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>1.56</v>
+        <v>2.85</v>
       </c>
       <c r="M283" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N283" t="n">
-        <v>5.4</v>
+        <v>2.38</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -37814,10 +37814,10 @@
         <v>0</v>
       </c>
       <c r="AB283" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC283" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD283" t="n">
         <v>0</v>
@@ -37862,7 +37862,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37872,12 +37872,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37898,13 +37898,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="M284" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N284" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37946,10 +37946,10 @@
         <v>0</v>
       </c>
       <c r="AB284" t="n">
-        <v>1.61</v>
+        <v>2.37</v>
       </c>
       <c r="AC284" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AD284" t="n">
         <v>0</v>
@@ -38004,12 +38004,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -38030,13 +38030,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>2.85</v>
+        <v>1.56</v>
       </c>
       <c r="M285" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N285" t="n">
-        <v>2.38</v>
+        <v>5.4</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -38078,10 +38078,10 @@
         <v>0</v>
       </c>
       <c r="AB285" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC285" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD285" t="n">
         <v>0</v>
@@ -38126,7 +38126,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -38136,12 +38136,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -38268,12 +38268,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -38390,7 +38390,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -38400,12 +38400,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -38426,13 +38426,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N288" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -38474,10 +38474,10 @@
         <v>0</v>
       </c>
       <c r="AB288" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC288" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD288" t="n">
         <v>0</v>
@@ -38522,7 +38522,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -38532,12 +38532,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -38654,7 +38654,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -38664,12 +38664,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -38690,13 +38690,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M290" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -38738,10 +38738,10 @@
         <v>0</v>
       </c>
       <c r="AB290" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC290" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD290" t="n">
         <v>0</v>
@@ -38796,12 +38796,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="M291" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N291" t="n">
-        <v>1.79</v>
+        <v>3.4</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -38870,10 +38870,10 @@
         <v>0</v>
       </c>
       <c r="AB291" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC291" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AD291" t="n">
         <v>0</v>
@@ -38928,12 +38928,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38954,13 +38954,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="M292" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N292" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -39002,16 +39002,16 @@
         <v>0</v>
       </c>
       <c r="AB292" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AE292" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC292" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD292" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE292" t="n">
-        <v>0</v>
       </c>
       <c r="AF292" t="n">
         <v>0</v>
@@ -39050,7 +39050,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -39060,12 +39060,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -39086,13 +39086,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M293" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -39134,10 +39134,10 @@
         <v>0</v>
       </c>
       <c r="AB293" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC293" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD293" t="n">
         <v>0</v>
@@ -39182,7 +39182,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -39192,12 +39192,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -39218,13 +39218,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N294" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -39266,10 +39266,10 @@
         <v>0</v>
       </c>
       <c r="AB294" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC294" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD294" t="n">
         <v>0</v>
@@ -39324,12 +39324,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -39350,13 +39350,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="M295" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N295" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -39398,16 +39398,16 @@
         <v>0</v>
       </c>
       <c r="AB295" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC295" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD295" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE295" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF295" t="n">
         <v>0</v>
@@ -39710,7 +39710,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -39720,12 +39720,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -39842,7 +39842,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -39852,12 +39852,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39974,7 +39974,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -39984,12 +39984,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -40010,13 +40010,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M300" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -40058,10 +40058,10 @@
         <v>0</v>
       </c>
       <c r="AB300" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC300" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD300" t="n">
         <v>0</v>
@@ -40106,7 +40106,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -40116,12 +40116,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -40142,13 +40142,13 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -40190,10 +40190,10 @@
         <v>0</v>
       </c>
       <c r="AB301" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC301" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD301" t="n">
         <v>0</v>

--- a/jogos_2025-08-09.xlsx
+++ b/jogos_2025-08-09.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.49</v>
+        <v>2.18</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8246,10 +8246,10 @@
         <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11472,12 +11472,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="M89" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N89" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,7 +12206,7 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC89" t="n">
         <v>1.7</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.36</v>
+        <v>1.97</v>
       </c>
       <c r="M95" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N95" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13706,22 +13706,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,22 +13838,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14534,13 +14534,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14582,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
         <v>0</v>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14798,13 +14798,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14846,10 +14846,10 @@
         <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD109" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,22 +15026,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,22 +15158,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16082,22 +16082,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.55</v>
+        <v>1.71</v>
       </c>
       <c r="M123" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N123" t="n">
-        <v>1.97</v>
+        <v>4.8</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17570,13 +17570,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17618,10 +17618,10 @@
         <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
         <v>0</v>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18626,13 +18626,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18674,10 +18674,10 @@
         <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD138" t="n">
         <v>0</v>
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.66</v>
+        <v>4</v>
       </c>
       <c r="M141" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N141" t="n">
-        <v>5.2</v>
+        <v>1.86</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19070,10 +19070,10 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AC141" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AD141" t="n">
         <v>0</v>
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -19202,10 +19202,10 @@
         <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
         <v>0</v>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19282,17 +19282,17 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -19334,10 +19334,10 @@
         <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
         <v>0</v>
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,22 +19778,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19862,10 +19862,10 @@
         <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC147" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD147" t="n">
         <v>0</v>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,22 +20042,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20126,10 +20126,10 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD149" t="n">
         <v>0</v>
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="M153" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="N153" t="n">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20654,10 +20654,10 @@
         <v>0</v>
       </c>
       <c r="AB153" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC153" t="n">
         <v>2.26</v>
-      </c>
-      <c r="AC153" t="n">
-        <v>1.54</v>
       </c>
       <c r="AD153" t="n">
         <v>0</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.62</v>
+        <v>1.66</v>
       </c>
       <c r="M154" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="N154" t="n">
-        <v>2.57</v>
+        <v>5.2</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20786,10 +20786,10 @@
         <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="AC154" t="n">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="AD154" t="n">
         <v>0</v>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20870,13 +20870,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.66</v>
+        <v>2.62</v>
       </c>
       <c r="M155" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="N155" t="n">
-        <v>5.2</v>
+        <v>2.57</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20918,10 +20918,10 @@
         <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.54</v>
+        <v>1.97</v>
       </c>
       <c r="AD155" t="n">
         <v>0</v>
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21002,13 +21002,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="M156" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N156" t="n">
-        <v>2.43</v>
+        <v>1.49</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -21044,16 +21044,16 @@
         <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC156" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD156" t="n">
         <v>0</v>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -21182,10 +21182,10 @@
         <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
         <v>0</v>
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21314,10 +21314,10 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21440,10 +21440,10 @@
         <v>0</v>
       </c>
       <c r="Z159" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB159" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21526,17 +21526,17 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21578,10 +21578,10 @@
         <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD160" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,10 +21710,10 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD161" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21974,10 +21974,10 @@
         <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC163" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD163" t="n">
         <v>0</v>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22454,13 +22454,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -22502,10 +22502,10 @@
         <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD167" t="n">
         <v>0</v>
@@ -22550,22 +22550,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22682,22 +22682,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22766,10 +22766,10 @@
         <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC169" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD169" t="n">
         <v>0</v>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,22 +23078,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23474,22 +23474,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23738,22 +23738,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23870,7 +23870,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,22 +24002,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,22 +24398,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24662,7 +24662,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24672,12 +24672,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24936,12 +24936,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25190,22 +25190,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25226,13 +25226,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AB188" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC188" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD188" t="n">
         <v>0</v>
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25358,13 +25358,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -25406,10 +25406,10 @@
         <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD189" t="n">
         <v>0</v>
@@ -25454,7 +25454,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25490,13 +25490,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -25544,10 +25544,10 @@
         <v>0</v>
       </c>
       <c r="AD190" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE190" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF190" t="n">
         <v>0</v>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25622,13 +25622,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25676,10 +25676,10 @@
         <v>0</v>
       </c>
       <c r="AD191" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE191" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF191" t="n">
         <v>0</v>
@@ -25850,7 +25850,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26018,13 +26018,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC198" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27038,22 +27038,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27434,22 +27434,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC205" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27566,22 +27566,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27830,22 +27830,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27962,7 +27962,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -28094,22 +28094,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28226,22 +28226,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="M212" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N212" t="n">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28442,10 +28442,10 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AC212" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AD212" t="n">
         <v>0</v>
@@ -28490,22 +28490,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28764,12 +28764,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28790,58 +28790,58 @@
         </is>
       </c>
       <c r="L215" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M215" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N215" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>0</v>
+      </c>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="n">
+        <v>0</v>
+      </c>
+      <c r="T215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="n">
+        <v>0</v>
+      </c>
+      <c r="V215" t="n">
+        <v>0</v>
+      </c>
+      <c r="W215" t="n">
+        <v>0</v>
+      </c>
+      <c r="X215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC215" t="n">
         <v>1.67</v>
-      </c>
-      <c r="M215" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N215" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O215" t="n">
-        <v>0</v>
-      </c>
-      <c r="P215" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0</v>
-      </c>
-      <c r="S215" t="n">
-        <v>0</v>
-      </c>
-      <c r="T215" t="n">
-        <v>0</v>
-      </c>
-      <c r="U215" t="n">
-        <v>0</v>
-      </c>
-      <c r="V215" t="n">
-        <v>0</v>
-      </c>
-      <c r="W215" t="n">
-        <v>0</v>
-      </c>
-      <c r="X215" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y215" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z215" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA215" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB215" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC215" t="n">
-        <v>2</v>
       </c>
       <c r="AD215" t="n">
         <v>0</v>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28922,13 +28922,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28970,10 +28970,10 @@
         <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC216" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD216" t="n">
         <v>0</v>
@@ -29028,12 +29028,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29057,10 +29057,10 @@
         <v>1.82</v>
       </c>
       <c r="M217" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N217" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29102,10 +29102,10 @@
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC217" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD217" t="n">
         <v>0</v>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29186,13 +29186,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -29234,10 +29234,10 @@
         <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC218" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD218" t="n">
         <v>0</v>
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -29556,12 +29556,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29762,10 +29762,10 @@
         <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC222" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
@@ -29810,7 +29810,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29820,12 +29820,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29846,13 +29846,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29894,10 +29894,10 @@
         <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD223" t="n">
         <v>0</v>
@@ -29942,22 +29942,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -30074,7 +30074,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -30084,12 +30084,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30374,13 +30374,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30602,7 +30602,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -30612,12 +30612,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30734,22 +30734,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30876,12 +30876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30902,13 +30902,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30944,10 +30944,10 @@
         <v>0</v>
       </c>
       <c r="Z231" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB231" t="n">
         <v>0</v>
@@ -30998,22 +30998,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -31034,13 +31034,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -31076,10 +31076,10 @@
         <v>0</v>
       </c>
       <c r="Z232" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA232" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB232" t="n">
         <v>0</v>
@@ -31130,7 +31130,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -31140,12 +31140,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -31166,13 +31166,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -31262,7 +31262,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -31272,12 +31272,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -31298,13 +31298,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -31394,22 +31394,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -31526,7 +31526,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -31536,12 +31536,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31658,22 +31658,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31790,22 +31790,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31868,10 +31868,10 @@
         <v>0</v>
       </c>
       <c r="Z238" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA238" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB238" t="n">
         <v>0</v>
@@ -31922,22 +31922,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31958,13 +31958,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -32000,10 +32000,10 @@
         <v>0</v>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA239" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB239" t="n">
         <v>0</v>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -32196,12 +32196,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32450,7 +32450,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -32460,12 +32460,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -32486,13 +32486,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N243" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -32540,10 +32540,10 @@
         <v>0</v>
       </c>
       <c r="AD243" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF243" t="n">
         <v>0</v>
@@ -32714,7 +32714,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -32724,12 +32724,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32750,13 +32750,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32804,10 +32804,10 @@
         <v>0</v>
       </c>
       <c r="AD245" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE245" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF245" t="n">
         <v>0</v>
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -33252,12 +33252,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -33384,12 +33384,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33648,12 +33648,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33780,12 +33780,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33912,12 +33912,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -34044,12 +34044,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -34430,7 +34430,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -34440,12 +34440,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -34466,13 +34466,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -34514,10 +34514,10 @@
         <v>0</v>
       </c>
       <c r="AB258" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC258" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD258" t="n">
         <v>0</v>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -34572,12 +34572,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -34598,13 +34598,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -34646,10 +34646,10 @@
         <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC259" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD259" t="n">
         <v>0</v>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -34704,12 +34704,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34836,12 +34836,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34862,13 +34862,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.37</v>
+        <v>2.25</v>
       </c>
       <c r="M261" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="N261" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34910,10 +34910,10 @@
         <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC261" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AD261" t="n">
         <v>0</v>
@@ -34968,12 +34968,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34994,13 +34994,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="M262" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="N262" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -35045,7 +35045,7 @@
         <v>2.3</v>
       </c>
       <c r="AC262" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD262" t="n">
         <v>0</v>
@@ -35100,12 +35100,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -35232,12 +35232,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -35364,12 +35364,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -35496,12 +35496,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -35618,7 +35618,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -35628,12 +35628,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -35760,12 +35760,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35882,7 +35882,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35892,12 +35892,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -36024,12 +36024,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -36156,12 +36156,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -36288,12 +36288,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -36542,7 +36542,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -36552,12 +36552,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -36684,12 +36684,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -36816,12 +36816,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36938,7 +36938,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36948,12 +36948,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -37202,7 +37202,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -37212,12 +37212,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -37238,13 +37238,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N279" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -37286,10 +37286,10 @@
         <v>0</v>
       </c>
       <c r="AB279" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC279" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD279" t="n">
         <v>0</v>
@@ -37334,7 +37334,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -37344,12 +37344,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -37370,13 +37370,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -37418,10 +37418,10 @@
         <v>0</v>
       </c>
       <c r="AB280" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC280" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD280" t="n">
         <v>0</v>
@@ -37466,7 +37466,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -37476,12 +37476,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -37502,13 +37502,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="M281" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N281" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -37550,10 +37550,10 @@
         <v>0</v>
       </c>
       <c r="AB281" t="n">
-        <v>1.61</v>
+        <v>2.37</v>
       </c>
       <c r="AC281" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AD281" t="n">
         <v>0</v>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -37608,12 +37608,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -37634,13 +37634,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -37682,10 +37682,10 @@
         <v>0</v>
       </c>
       <c r="AB282" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC282" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD282" t="n">
         <v>0</v>
@@ -37740,12 +37740,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37766,13 +37766,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="M283" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N283" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -37814,10 +37814,10 @@
         <v>0</v>
       </c>
       <c r="AB283" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC283" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD283" t="n">
         <v>0</v>
@@ -37862,7 +37862,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37872,12 +37872,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37898,13 +37898,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37946,10 +37946,10 @@
         <v>0</v>
       </c>
       <c r="AB284" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC284" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD284" t="n">
         <v>0</v>
@@ -38004,12 +38004,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -38030,13 +38030,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.56</v>
+        <v>2.19</v>
       </c>
       <c r="M285" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N285" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -38126,7 +38126,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -38136,12 +38136,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -38162,13 +38162,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -38210,10 +38210,10 @@
         <v>0</v>
       </c>
       <c r="AB286" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC286" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD286" t="n">
         <v>0</v>
@@ -38258,7 +38258,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -38268,12 +38268,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -38390,7 +38390,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -38400,12 +38400,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -38532,12 +38532,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -38654,7 +38654,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -38664,12 +38664,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -38690,13 +38690,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N290" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -38738,10 +38738,10 @@
         <v>0</v>
       </c>
       <c r="AB290" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC290" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD290" t="n">
         <v>0</v>
@@ -38796,12 +38796,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="M291" t="n">
         <v>3.25</v>
       </c>
       <c r="N291" t="n">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -38870,16 +38870,16 @@
         <v>0</v>
       </c>
       <c r="AB291" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AC291" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD291" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE291" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF291" t="n">
         <v>0</v>
@@ -38928,12 +38928,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38954,13 +38954,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="M292" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N292" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -39002,16 +39002,16 @@
         <v>0</v>
       </c>
       <c r="AB292" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC292" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD292" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE292" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF292" t="n">
         <v>0</v>
@@ -39050,7 +39050,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -39060,12 +39060,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -39086,13 +39086,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N293" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -39134,10 +39134,10 @@
         <v>0</v>
       </c>
       <c r="AB293" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC293" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD293" t="n">
         <v>0</v>
@@ -39182,7 +39182,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -39192,12 +39192,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -39218,13 +39218,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -39266,10 +39266,10 @@
         <v>0</v>
       </c>
       <c r="AB294" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC294" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD294" t="n">
         <v>0</v>
@@ -39974,7 +39974,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -39984,12 +39984,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -40010,13 +40010,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N300" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -40058,10 +40058,10 @@
         <v>0</v>
       </c>
       <c r="AB300" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC300" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD300" t="n">
         <v>0</v>
@@ -40106,7 +40106,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -40116,12 +40116,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -40142,13 +40142,13 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M301" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N301" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -40190,10 +40190,10 @@
         <v>0</v>
       </c>
       <c r="AB301" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC301" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD301" t="n">
         <v>0</v>

--- a/jogos_2025-08-09.xlsx
+++ b/jogos_2025-08-09.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,22 +6974,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,22 +7370,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7670,13 +7670,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,22 +10934,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12158,13 +12158,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -12206,10 +12206,10 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13706,22 +13706,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="M112" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N112" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15245,7 +15245,7 @@
         <v>2.15</v>
       </c>
       <c r="AC112" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15554,22 +15554,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,22 +15686,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="M122" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N122" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="M123" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N123" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16874,22 +16874,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,22 +17138,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC132" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC134" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,22 +18194,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,10 +18806,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD139" t="n">
         <v>0</v>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC140" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19022,13 +19022,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -19070,10 +19070,10 @@
         <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD141" t="n">
         <v>0</v>
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,22 +19778,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="M147" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="N147" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19862,10 +19862,10 @@
         <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AC147" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AD147" t="n">
         <v>0</v>
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,7 +20042,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20602,17 +20602,17 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20654,10 +20654,10 @@
         <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD153" t="n">
         <v>0</v>
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.66</v>
+        <v>1.13</v>
       </c>
       <c r="M154" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="N154" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20786,10 +20786,10 @@
         <v>0</v>
       </c>
       <c r="AB154" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC154" t="n">
         <v>2.26</v>
-      </c>
-      <c r="AC154" t="n">
-        <v>1.54</v>
       </c>
       <c r="AD154" t="n">
         <v>0</v>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20870,13 +20870,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.62</v>
+        <v>1.66</v>
       </c>
       <c r="M155" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="N155" t="n">
-        <v>2.57</v>
+        <v>5.2</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20918,10 +20918,10 @@
         <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="AD155" t="n">
         <v>0</v>
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21002,13 +21002,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>5.8</v>
+        <v>2.7</v>
       </c>
       <c r="M156" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N156" t="n">
-        <v>1.49</v>
+        <v>2.43</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -21044,16 +21044,16 @@
         <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD156" t="n">
         <v>0</v>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -21182,10 +21182,10 @@
         <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD157" t="n">
         <v>0</v>
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21314,10 +21314,10 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD158" t="n">
         <v>0</v>
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="M159" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N159" t="n">
-        <v>2.43</v>
+        <v>1.49</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21440,16 +21440,16 @@
         <v>0</v>
       </c>
       <c r="Z159" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD159" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="M160" t="n">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="N160" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21578,10 +21578,10 @@
         <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="AC160" t="n">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="AD160" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,10 +21710,10 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21842,10 +21842,10 @@
         <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC162" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD162" t="n">
         <v>0</v>
@@ -21890,22 +21890,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="M163" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N163" t="n">
-        <v>4.3</v>
+        <v>3.56</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21974,10 +21974,10 @@
         <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AC163" t="n">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AD163" t="n">
         <v>0</v>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22154,22 +22154,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="M166" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N166" t="n">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,10 +22370,10 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC166" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD166" t="n">
         <v>0</v>
@@ -22550,22 +22550,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22682,7 +22682,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22692,12 +22692,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="M169" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N169" t="n">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22766,10 +22766,10 @@
         <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD169" t="n">
         <v>0</v>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,22 +23078,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23738,22 +23738,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23870,22 +23870,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,22 +24398,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -25068,12 +25068,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25322,7 +25322,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -25332,12 +25332,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25538,10 +25538,10 @@
         <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC190" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD190" t="n">
         <v>2.1</v>
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25754,13 +25754,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="M192" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N192" t="n">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25802,10 +25802,10 @@
         <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC192" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD192" t="n">
         <v>0</v>
@@ -25850,22 +25850,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="M193" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N193" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25934,10 +25934,10 @@
         <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC193" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD193" t="n">
         <v>0</v>
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC201" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27038,22 +27038,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27434,22 +27434,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27650,10 +27650,10 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC206" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -27698,7 +27698,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27830,22 +27830,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27962,22 +27962,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28226,22 +28226,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC211" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="M212" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N212" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28764,12 +28764,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28790,13 +28790,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28838,10 +28838,10 @@
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC215" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD215" t="n">
         <v>0</v>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28922,13 +28922,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28970,10 +28970,10 @@
         <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC216" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD216" t="n">
         <v>0</v>
@@ -29018,7 +29018,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29102,10 +29102,10 @@
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD217" t="n">
         <v>0</v>
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29556,12 +29556,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>3.15</v>
+        <v>1.82</v>
       </c>
       <c r="M222" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N222" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29762,10 +29762,10 @@
         <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AC222" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
@@ -29810,22 +29810,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29942,7 +29942,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29952,12 +29952,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -30074,7 +30074,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -30084,12 +30084,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30110,13 +30110,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30602,7 +30602,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -30612,12 +30612,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30734,7 +30734,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30744,12 +30744,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30866,22 +30866,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30902,13 +30902,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30998,22 +30998,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -31034,13 +31034,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -31076,10 +31076,10 @@
         <v>0</v>
       </c>
       <c r="Z232" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA232" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB232" t="n">
         <v>0</v>
@@ -31130,22 +31130,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -31166,13 +31166,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="M233" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N233" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -31208,10 +31208,10 @@
         <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA233" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB233" t="n">
         <v>0</v>
@@ -31262,22 +31262,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -31394,7 +31394,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -31404,12 +31404,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -31526,22 +31526,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31668,12 +31668,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31694,13 +31694,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31736,10 +31736,10 @@
         <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA237" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB237" t="n">
         <v>0</v>
@@ -31790,22 +31790,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31922,7 +31922,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31932,12 +31932,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31958,13 +31958,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -32000,10 +32000,10 @@
         <v>0</v>
       </c>
       <c r="Z239" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA239" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB239" t="n">
         <v>0</v>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -32196,12 +32196,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -32592,12 +32592,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -32714,22 +32714,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32750,13 +32750,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32804,10 +32804,10 @@
         <v>0</v>
       </c>
       <c r="AD245" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF245" t="n">
         <v>0</v>
@@ -32846,22 +32846,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32882,13 +32882,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32930,16 +32930,16 @@
         <v>0</v>
       </c>
       <c r="AB246" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC246" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD246" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE246" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF246" t="n">
         <v>0</v>
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -33252,12 +33252,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -33384,12 +33384,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33648,12 +33648,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33780,12 +33780,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33912,12 +33912,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -34044,12 +34044,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -34176,12 +34176,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -34430,7 +34430,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -34440,12 +34440,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -34466,13 +34466,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -34514,10 +34514,10 @@
         <v>0</v>
       </c>
       <c r="AB258" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC258" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD258" t="n">
         <v>0</v>
@@ -34562,7 +34562,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -34572,12 +34572,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -34598,13 +34598,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -34646,10 +34646,10 @@
         <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC259" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD259" t="n">
         <v>0</v>
@@ -35100,12 +35100,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -35222,7 +35222,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -35232,12 +35232,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -35364,12 +35364,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -35496,12 +35496,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -35618,7 +35618,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -35628,12 +35628,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -35760,12 +35760,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35892,12 +35892,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -36024,12 +36024,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -36156,12 +36156,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -36288,12 +36288,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -36542,7 +36542,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -36552,12 +36552,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -36816,12 +36816,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36948,12 +36948,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -37202,7 +37202,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -37212,12 +37212,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -37238,13 +37238,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -37286,10 +37286,10 @@
         <v>0</v>
       </c>
       <c r="AB279" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC279" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD279" t="n">
         <v>0</v>
@@ -37344,12 +37344,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -37370,13 +37370,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>1.56</v>
+        <v>2.19</v>
       </c>
       <c r="M280" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N280" t="n">
-        <v>5.4</v>
+        <v>3.2</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -37466,7 +37466,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -37476,12 +37476,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -37502,13 +37502,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>2.8</v>
+        <v>1.56</v>
       </c>
       <c r="M281" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="N281" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -37550,10 +37550,10 @@
         <v>0</v>
       </c>
       <c r="AB281" t="n">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="AC281" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AD281" t="n">
         <v>0</v>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -37608,12 +37608,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -37634,13 +37634,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="M282" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N282" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -37682,10 +37682,10 @@
         <v>0</v>
       </c>
       <c r="AB282" t="n">
-        <v>1.6</v>
+        <v>2.37</v>
       </c>
       <c r="AC282" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AD282" t="n">
         <v>0</v>
@@ -37740,12 +37740,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37766,13 +37766,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="M283" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N283" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -37814,10 +37814,10 @@
         <v>0</v>
       </c>
       <c r="AB283" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC283" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD283" t="n">
         <v>0</v>
@@ -37862,7 +37862,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37872,12 +37872,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -38004,12 +38004,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -38030,13 +38030,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -38078,10 +38078,10 @@
         <v>0</v>
       </c>
       <c r="AB285" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC285" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD285" t="n">
         <v>0</v>
@@ -38268,12 +38268,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -38400,12 +38400,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -38522,7 +38522,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -38532,12 +38532,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -38654,7 +38654,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -38664,12 +38664,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -38796,12 +38796,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="M291" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N291" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -38870,16 +38870,16 @@
         <v>0</v>
       </c>
       <c r="AB291" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC291" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD291" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE291" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF291" t="n">
         <v>0</v>
@@ -39050,7 +39050,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -39060,12 +39060,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -39086,13 +39086,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M293" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -39134,10 +39134,10 @@
         <v>0</v>
       </c>
       <c r="AB293" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC293" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD293" t="n">
         <v>0</v>
@@ -39182,7 +39182,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -39192,12 +39192,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -39218,13 +39218,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N294" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -39266,10 +39266,10 @@
         <v>0</v>
       </c>
       <c r="AB294" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC294" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD294" t="n">
         <v>0</v>
@@ -39324,12 +39324,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -39350,13 +39350,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="M295" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N295" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -39398,16 +39398,16 @@
         <v>0</v>
       </c>
       <c r="AB295" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC295" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD295" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE295" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF295" t="n">
         <v>0</v>
@@ -39710,7 +39710,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -39720,12 +39720,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -39842,7 +39842,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -39852,12 +39852,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G299" t="n">

--- a/jogos_2025-08-09.xlsx
+++ b/jogos_2025-08-09.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.75</v>
+        <v>1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>2.37</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,22 +8294,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9218,22 +9218,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,22 +9350,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9962,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="M85" t="n">
-        <v>3.12</v>
+        <v>3.83</v>
       </c>
       <c r="N85" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,22 +13442,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15194,13 +15194,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -15242,10 +15242,10 @@
         <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,22 +15686,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15770,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD116" t="n">
         <v>0</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="M119" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N119" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="M120" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N120" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.77</v>
+        <v>1.39</v>
       </c>
       <c r="M121" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N121" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,7 +16430,7 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC121" t="n">
         <v>1.7</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="M122" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N122" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>2.15</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16646,13 +16646,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16694,10 +16694,10 @@
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16874,22 +16874,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17702,13 +17702,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -17798,22 +17798,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17834,13 +17834,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17882,10 +17882,10 @@
         <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17966,13 +17966,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -18014,10 +18014,10 @@
         <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,10 +18806,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC139" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD139" t="n">
         <v>0</v>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.47</v>
+        <v>1.46</v>
       </c>
       <c r="M140" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="N140" t="n">
-        <v>2.85</v>
+        <v>6.4</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC140" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19466,10 +19466,10 @@
         <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC144" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD144" t="n">
         <v>0</v>
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19598,10 +19598,10 @@
         <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC145" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD145" t="n">
         <v>0</v>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19862,10 +19862,10 @@
         <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD147" t="n">
         <v>0</v>
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -20042,22 +20042,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20126,10 +20126,10 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC149" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD149" t="n">
         <v>0</v>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20210,13 +20210,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -20252,10 +20252,10 @@
         <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA150" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB150" t="n">
         <v>0</v>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20786,10 +20786,10 @@
         <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD154" t="n">
         <v>0</v>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20870,13 +20870,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.66</v>
+        <v>2.62</v>
       </c>
       <c r="M155" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="N155" t="n">
-        <v>5.2</v>
+        <v>2.57</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20918,10 +20918,10 @@
         <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.54</v>
+        <v>1.97</v>
       </c>
       <c r="AD155" t="n">
         <v>0</v>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21002,13 +21002,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -21044,10 +21044,10 @@
         <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
         <v>0</v>
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>3.94</v>
+        <v>5.8</v>
       </c>
       <c r="M157" t="n">
-        <v>3.11</v>
+        <v>3.9</v>
       </c>
       <c r="N157" t="n">
-        <v>1.84</v>
+        <v>1.49</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -21182,10 +21182,10 @@
         <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AD157" t="n">
         <v>0</v>
@@ -21230,7 +21230,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21240,12 +21240,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21314,10 +21314,10 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
         <v>0</v>
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>5.8</v>
+        <v>1.66</v>
       </c>
       <c r="M159" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N159" t="n">
-        <v>1.49</v>
+        <v>5.2</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21446,10 +21446,10 @@
         <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AC159" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AD159" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.62</v>
+        <v>1.13</v>
       </c>
       <c r="M160" t="n">
-        <v>3.54</v>
+        <v>6.8</v>
       </c>
       <c r="N160" t="n">
-        <v>2.57</v>
+        <v>16</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21578,10 +21578,10 @@
         <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="AC160" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="AD160" t="n">
         <v>0</v>
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.39</v>
+        <v>3.94</v>
       </c>
       <c r="M162" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="N162" t="n">
-        <v>2.66</v>
+        <v>1.84</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21842,10 +21842,10 @@
         <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AC162" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AD162" t="n">
         <v>0</v>
@@ -21890,22 +21890,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21974,10 +21974,10 @@
         <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD163" t="n">
         <v>0</v>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22058,13 +22058,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -22106,10 +22106,10 @@
         <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC164" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD164" t="n">
         <v>0</v>
@@ -22154,22 +22154,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="M166" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N166" t="n">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,10 +22370,10 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD166" t="n">
         <v>0</v>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22634,10 +22634,10 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD168" t="n">
         <v>0</v>
@@ -22682,22 +22682,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,22 +23078,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23342,22 +23342,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23474,22 +23474,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23606,22 +23606,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23870,22 +23870,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,22 +24398,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24662,22 +24662,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24694,17 +24694,17 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24740,10 +24740,10 @@
         <v>0</v>
       </c>
       <c r="Z184" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA184" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB184" t="n">
         <v>0</v>
@@ -24794,22 +24794,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24826,17 +24826,17 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24872,10 +24872,10 @@
         <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
         <v>0</v>
@@ -25058,22 +25058,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25142,10 +25142,10 @@
         <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC187" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD187" t="n">
         <v>0</v>
@@ -25190,22 +25190,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25226,13 +25226,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AB188" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC188" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD188" t="n">
         <v>0</v>
@@ -25322,7 +25322,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -25332,12 +25332,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25850,22 +25850,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25934,10 +25934,10 @@
         <v>0</v>
       </c>
       <c r="AB193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC193" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD193" t="n">
         <v>0</v>
@@ -25982,22 +25982,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26018,13 +26018,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -26066,10 +26066,10 @@
         <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC194" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD194" t="n">
         <v>0</v>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC196" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AC201" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27170,22 +27170,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27434,22 +27434,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27602,13 +27602,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27650,10 +27650,10 @@
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD206" t="n">
         <v>0</v>
@@ -27698,7 +27698,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27782,10 +27782,10 @@
         <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC207" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD207" t="n">
         <v>0</v>
@@ -27830,22 +27830,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27866,13 +27866,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27914,10 +27914,10 @@
         <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC208" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD208" t="n">
         <v>0</v>
@@ -27962,22 +27962,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC210" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="M211" t="n">
         <v>3.3</v>
       </c>
       <c r="N211" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC211" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28442,10 +28442,10 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD212" t="n">
         <v>0</v>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28526,13 +28526,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -28574,10 +28574,10 @@
         <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD213" t="n">
         <v>0</v>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28754,22 +28754,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -29028,12 +29028,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -29556,12 +29556,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="M222" t="n">
         <v>3.35</v>
       </c>
       <c r="N222" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29810,7 +29810,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29820,12 +29820,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29942,22 +29942,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -30026,10 +30026,10 @@
         <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD224" t="n">
         <v>0</v>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -30084,12 +30084,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30110,13 +30110,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30602,7 +30602,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -30612,12 +30612,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30734,22 +30734,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30876,12 +30876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30902,13 +30902,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30998,22 +30998,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -31130,22 +31130,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -31166,13 +31166,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -31208,10 +31208,10 @@
         <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA233" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB233" t="n">
         <v>0</v>
@@ -31272,12 +31272,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -31298,13 +31298,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -31340,10 +31340,10 @@
         <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA234" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB234" t="n">
         <v>0</v>
@@ -31394,22 +31394,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -31526,7 +31526,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -31536,12 +31536,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31668,12 +31668,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31694,13 +31694,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="M237" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N237" t="n">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31736,10 +31736,10 @@
         <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA237" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB237" t="n">
         <v>0</v>
@@ -31790,22 +31790,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31922,22 +31922,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -32196,12 +32196,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32450,22 +32450,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -32582,22 +32582,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M244" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -32666,16 +32666,16 @@
         <v>0</v>
       </c>
       <c r="AB244" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC244" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD244" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE244" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF244" t="n">
         <v>0</v>
@@ -32714,22 +32714,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32846,22 +32846,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32882,13 +32882,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N246" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32930,16 +32930,16 @@
         <v>0</v>
       </c>
       <c r="AB246" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC246" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD246" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF246" t="n">
         <v>0</v>
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -33384,12 +33384,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -33648,12 +33648,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33912,12 +33912,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -34044,12 +34044,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -34176,12 +34176,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -34430,7 +34430,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -34440,12 +34440,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -34562,7 +34562,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -34572,12 +34572,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -34598,13 +34598,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -34646,10 +34646,10 @@
         <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC259" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD259" t="n">
         <v>0</v>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -34704,12 +34704,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34730,13 +34730,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -34778,10 +34778,10 @@
         <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC260" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD260" t="n">
         <v>0</v>
@@ -34836,12 +34836,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34862,13 +34862,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="M261" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="N261" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34913,7 +34913,7 @@
         <v>2.3</v>
       </c>
       <c r="AC261" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD261" t="n">
         <v>0</v>
@@ -34968,12 +34968,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34994,13 +34994,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="M262" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N262" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -35042,10 +35042,10 @@
         <v>0</v>
       </c>
       <c r="AB262" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC262" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD262" t="n">
         <v>0</v>
@@ -35090,7 +35090,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -35100,12 +35100,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -35232,12 +35232,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -35354,7 +35354,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -35364,12 +35364,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -35618,7 +35618,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -35628,12 +35628,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -35760,12 +35760,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35892,12 +35892,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -36014,7 +36014,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -36024,12 +36024,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -36146,7 +36146,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -36156,12 +36156,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -36278,7 +36278,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -36288,12 +36288,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -36552,12 +36552,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -36816,12 +36816,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -37070,7 +37070,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -37080,12 +37080,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -37344,12 +37344,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -37370,13 +37370,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.19</v>
+        <v>2.85</v>
       </c>
       <c r="M280" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N280" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -37418,10 +37418,10 @@
         <v>0</v>
       </c>
       <c r="AB280" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC280" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD280" t="n">
         <v>0</v>
@@ -37466,7 +37466,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -37476,12 +37476,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -37502,13 +37502,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N281" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -37550,10 +37550,10 @@
         <v>0</v>
       </c>
       <c r="AB281" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC281" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD281" t="n">
         <v>0</v>
@@ -37740,12 +37740,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37766,14 +37766,14 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>2.85</v>
+        <v>2.19</v>
       </c>
       <c r="M283" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N283" t="n">
         <v>3.2</v>
       </c>
-      <c r="N283" t="n">
-        <v>2.38</v>
-      </c>
       <c r="O283" t="n">
         <v>0</v>
       </c>
@@ -37814,10 +37814,10 @@
         <v>0</v>
       </c>
       <c r="AB283" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC283" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD283" t="n">
         <v>0</v>
@@ -37862,7 +37862,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37872,12 +37872,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37898,13 +37898,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37946,10 +37946,10 @@
         <v>0</v>
       </c>
       <c r="AB284" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC284" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD284" t="n">
         <v>0</v>
@@ -37994,7 +37994,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -38004,12 +38004,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -38126,7 +38126,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -38136,12 +38136,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -38162,13 +38162,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -38210,10 +38210,10 @@
         <v>0</v>
       </c>
       <c r="AB286" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC286" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD286" t="n">
         <v>0</v>
@@ -38258,7 +38258,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -38268,12 +38268,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -38294,13 +38294,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -38342,10 +38342,10 @@
         <v>0</v>
       </c>
       <c r="AB287" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC287" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD287" t="n">
         <v>0</v>
@@ -38532,12 +38532,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -38654,7 +38654,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -38664,12 +38664,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -38786,7 +38786,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -38796,12 +38796,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N291" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -38870,10 +38870,10 @@
         <v>0</v>
       </c>
       <c r="AB291" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC291" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD291" t="n">
         <v>0</v>
@@ -38928,12 +38928,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38954,13 +38954,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="M292" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N292" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -39002,10 +39002,10 @@
         <v>0</v>
       </c>
       <c r="AB292" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC292" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD292" t="n">
         <v>0</v>
@@ -39060,12 +39060,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -39086,13 +39086,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="M293" t="n">
         <v>3.25</v>
       </c>
       <c r="N293" t="n">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -39134,16 +39134,16 @@
         <v>0</v>
       </c>
       <c r="AB293" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AC293" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD293" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE293" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF293" t="n">
         <v>0</v>
@@ -39182,7 +39182,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -39192,12 +39192,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -39218,13 +39218,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -39266,10 +39266,10 @@
         <v>0</v>
       </c>
       <c r="AB294" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC294" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD294" t="n">
         <v>0</v>
@@ -39324,12 +39324,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -39350,13 +39350,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="M295" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N295" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -39398,16 +39398,16 @@
         <v>0</v>
       </c>
       <c r="AB295" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC295" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD295" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE295" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF295" t="n">
         <v>0</v>
@@ -39578,7 +39578,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -39588,12 +39588,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -39842,7 +39842,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -39852,12 +39852,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39974,7 +39974,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -39984,12 +39984,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -40010,13 +40010,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M300" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -40058,10 +40058,10 @@
         <v>0</v>
       </c>
       <c r="AB300" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC300" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD300" t="n">
         <v>0</v>
@@ -40106,7 +40106,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -40116,12 +40116,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -40142,13 +40142,13 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -40190,10 +40190,10 @@
         <v>0</v>
       </c>
       <c r="AB301" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC301" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD301" t="n">
         <v>0</v>

--- a/jogos_2025-08-09.xlsx
+++ b/jogos_2025-08-09.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1865,10 +1865,10 @@
         <v>1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="N17" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.49</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>1.9</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="M20" t="n">
         <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8030,22 +8030,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,22 +8162,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,22 +8294,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8426,22 +8426,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,22 +9614,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9830,10 +9830,10 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10670,22 +10670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11282,10 +11282,10 @@
         <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
         <v>0</v>
@@ -11330,22 +11330,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,22 +12254,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,22 +12518,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,22 +12650,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,22 +12914,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13214,13 +13214,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13262,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14318,10 +14318,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15686,22 +15686,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15770,10 +15770,10 @@
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
         <v>0</v>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -16298,10 +16298,10 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16430,10 +16430,10 @@
         <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
         <v>0</v>
@@ -16478,7 +16478,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16514,13 +16514,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16562,10 +16562,10 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
         <v>0</v>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.55</v>
+        <v>1.77</v>
       </c>
       <c r="M124" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N124" t="n">
-        <v>1.97</v>
+        <v>4.4</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AC124" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17222,10 +17222,10 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17280,12 +17280,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17930,22 +17930,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18072,12 +18072,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC134" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC136" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.47</v>
+        <v>1.46</v>
       </c>
       <c r="M139" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="N139" t="n">
-        <v>2.85</v>
+        <v>6.4</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,10 +18806,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC139" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD139" t="n">
         <v>0</v>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.46</v>
+        <v>2.47</v>
       </c>
       <c r="M140" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="N140" t="n">
-        <v>6.4</v>
+        <v>2.85</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC140" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19466,10 +19466,10 @@
         <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD144" t="n">
         <v>0</v>
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19598,10 +19598,10 @@
         <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD145" t="n">
         <v>0</v>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L148" t="n">
@@ -20042,22 +20042,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20126,10 +20126,10 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD149" t="n">
         <v>0</v>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20210,13 +20210,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -20252,10 +20252,10 @@
         <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB150" t="n">
         <v>0</v>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20474,13 +20474,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20522,10 +20522,10 @@
         <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC152" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD152" t="n">
         <v>0</v>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20654,10 +20654,10 @@
         <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC153" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD153" t="n">
         <v>0</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20786,10 +20786,10 @@
         <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC154" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD154" t="n">
         <v>0</v>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20870,13 +20870,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="M155" t="n">
-        <v>3.54</v>
+        <v>3.29</v>
       </c>
       <c r="N155" t="n">
-        <v>2.57</v>
+        <v>4.2</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20918,10 +20918,10 @@
         <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.83</v>
+        <v>2.26</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="AD155" t="n">
         <v>0</v>
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>5.8</v>
+        <v>1.13</v>
       </c>
       <c r="M157" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="N157" t="n">
-        <v>1.49</v>
+        <v>16</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -21182,10 +21182,10 @@
         <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.72</v>
+        <v>2.26</v>
       </c>
       <c r="AD157" t="n">
         <v>0</v>
@@ -21230,22 +21230,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21314,10 +21314,10 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD158" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21398,13 +21398,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -21446,10 +21446,10 @@
         <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
         <v>0</v>
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.13</v>
+        <v>1.66</v>
       </c>
       <c r="M160" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="N160" t="n">
-        <v>16</v>
+        <v>5.2</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21578,10 +21578,10 @@
         <v>0</v>
       </c>
       <c r="AB160" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC160" t="n">
         <v>1.54</v>
-      </c>
-      <c r="AC160" t="n">
-        <v>2.26</v>
       </c>
       <c r="AD160" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,10 +21710,10 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD161" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21842,10 +21842,10 @@
         <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD162" t="n">
         <v>0</v>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21974,10 +21974,10 @@
         <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC163" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD163" t="n">
         <v>0</v>
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22058,13 +22058,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="M164" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N164" t="n">
-        <v>5.2</v>
+        <v>2.43</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -22100,16 +22100,16 @@
         <v>0</v>
       </c>
       <c r="Z164" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB164" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD164" t="n">
         <v>0</v>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="M166" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N166" t="n">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,10 +22370,10 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC166" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD166" t="n">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22428,12 +22428,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22454,13 +22454,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22634,10 +22634,10 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC168" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD168" t="n">
         <v>0</v>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23342,22 +23342,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23474,22 +23474,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23606,22 +23606,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23870,7 +23870,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23880,12 +23880,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -24144,12 +24144,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -24276,12 +24276,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24662,22 +24662,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24694,17 +24694,17 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24740,10 +24740,10 @@
         <v>0</v>
       </c>
       <c r="Z184" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB184" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24926,22 +24926,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24958,17 +24958,17 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -25004,10 +25004,10 @@
         <v>0</v>
       </c>
       <c r="Z186" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB186" t="n">
         <v>0</v>
@@ -25058,22 +25058,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25142,10 +25142,10 @@
         <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC187" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD187" t="n">
         <v>0</v>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -25200,12 +25200,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25358,13 +25358,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -25406,10 +25406,10 @@
         <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC189" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD189" t="n">
         <v>0</v>
@@ -25718,22 +25718,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25754,13 +25754,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="M192" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N192" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25802,10 +25802,10 @@
         <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC192" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD192" t="n">
         <v>0</v>
@@ -25850,7 +25850,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25982,22 +25982,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26018,13 +26018,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -26066,10 +26066,10 @@
         <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC194" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD194" t="n">
         <v>0</v>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -26256,12 +26256,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26282,13 +26282,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD196" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -26388,12 +26388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC197" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD197" t="n">
         <v>0</v>
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27038,7 +27038,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC202" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27170,22 +27170,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27302,22 +27302,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27566,7 +27566,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27698,22 +27698,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27734,13 +27734,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27782,10 +27782,10 @@
         <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC207" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD207" t="n">
         <v>0</v>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27840,12 +27840,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27866,13 +27866,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27914,10 +27914,10 @@
         <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AC208" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD208" t="n">
         <v>0</v>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28046,10 +28046,10 @@
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC209" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD209" t="n">
         <v>0</v>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC210" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28368,12 +28368,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28442,10 +28442,10 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC212" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD212" t="n">
         <v>0</v>
@@ -28754,22 +28754,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28790,13 +28790,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28838,10 +28838,10 @@
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC215" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD215" t="n">
         <v>0</v>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -29018,22 +29018,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29556,12 +29556,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,58 +29714,58 @@
         </is>
       </c>
       <c r="L222" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M222" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N222" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
+        <v>0</v>
+      </c>
+      <c r="U222" t="n">
+        <v>0</v>
+      </c>
+      <c r="V222" t="n">
+        <v>0</v>
+      </c>
+      <c r="W222" t="n">
+        <v>0</v>
+      </c>
+      <c r="X222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC222" t="n">
         <v>2</v>
-      </c>
-      <c r="M222" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N222" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O222" t="n">
-        <v>0</v>
-      </c>
-      <c r="P222" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
-      <c r="S222" t="n">
-        <v>0</v>
-      </c>
-      <c r="T222" t="n">
-        <v>0</v>
-      </c>
-      <c r="U222" t="n">
-        <v>0</v>
-      </c>
-      <c r="V222" t="n">
-        <v>0</v>
-      </c>
-      <c r="W222" t="n">
-        <v>0</v>
-      </c>
-      <c r="X222" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y222" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z222" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA222" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB222" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC222" t="n">
-        <v>1.8</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
@@ -29810,22 +29810,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29942,7 +29942,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29952,12 +29952,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -30026,10 +30026,10 @@
         <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD224" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30602,22 +30602,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30638,13 +30638,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -30680,10 +30680,10 @@
         <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB229" t="n">
         <v>0</v>
@@ -30734,22 +30734,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30876,12 +30876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -31008,12 +31008,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -31130,22 +31130,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -31272,12 +31272,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -31298,13 +31298,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -31340,10 +31340,10 @@
         <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA234" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB234" t="n">
         <v>0</v>
@@ -31394,22 +31394,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -31658,22 +31658,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31694,13 +31694,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N237" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31736,10 +31736,10 @@
         <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA237" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB237" t="n">
         <v>0</v>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31800,12 +31800,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31826,13 +31826,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31932,12 +31932,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31958,13 +31958,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -32186,22 +32186,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32222,13 +32222,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -32264,10 +32264,10 @@
         <v>0</v>
       </c>
       <c r="Z241" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA241" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB241" t="n">
         <v>0</v>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -32592,12 +32592,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -32666,16 +32666,16 @@
         <v>0</v>
       </c>
       <c r="AB244" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC244" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD244" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF244" t="n">
         <v>0</v>
@@ -32714,7 +32714,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -32724,12 +32724,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32750,13 +32750,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32798,16 +32798,16 @@
         <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC245" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD245" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE245" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF245" t="n">
         <v>0</v>
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -33252,12 +33252,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33648,12 +33648,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33780,12 +33780,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33912,12 +33912,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -34044,12 +34044,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -34176,12 +34176,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -34562,7 +34562,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -34572,12 +34572,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -34598,13 +34598,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -34646,10 +34646,10 @@
         <v>0</v>
       </c>
       <c r="AB259" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC259" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD259" t="n">
         <v>0</v>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -34704,12 +34704,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34730,13 +34730,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -34778,10 +34778,10 @@
         <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC260" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD260" t="n">
         <v>0</v>
@@ -35090,7 +35090,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -35100,12 +35100,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -35222,7 +35222,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -35232,12 +35232,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -35364,12 +35364,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -35496,12 +35496,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -35628,12 +35628,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -35760,12 +35760,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35882,7 +35882,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35892,12 +35892,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -36024,12 +36024,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -36156,12 +36156,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -36278,7 +36278,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -36288,12 +36288,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -36552,12 +36552,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -36684,12 +36684,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -36816,12 +36816,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36948,12 +36948,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -37070,7 +37070,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -37080,12 +37080,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -37212,12 +37212,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -37238,13 +37238,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="M279" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N279" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -37286,10 +37286,10 @@
         <v>0</v>
       </c>
       <c r="AB279" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC279" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD279" t="n">
         <v>0</v>
@@ -37344,12 +37344,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -37370,13 +37370,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.85</v>
+        <v>1.56</v>
       </c>
       <c r="M280" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N280" t="n">
-        <v>2.38</v>
+        <v>5.4</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -37418,10 +37418,10 @@
         <v>0</v>
       </c>
       <c r="AB280" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC280" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD280" t="n">
         <v>0</v>
@@ -37466,7 +37466,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -37476,12 +37476,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -37502,13 +37502,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -37550,10 +37550,10 @@
         <v>0</v>
       </c>
       <c r="AB281" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC281" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD281" t="n">
         <v>0</v>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -37608,12 +37608,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -37634,13 +37634,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -37682,10 +37682,10 @@
         <v>0</v>
       </c>
       <c r="AB282" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC282" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD282" t="n">
         <v>0</v>
@@ -37730,7 +37730,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -37740,12 +37740,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37766,13 +37766,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N283" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -37814,10 +37814,10 @@
         <v>0</v>
       </c>
       <c r="AB283" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC283" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD283" t="n">
         <v>0</v>
@@ -37872,12 +37872,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37898,13 +37898,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.56</v>
+        <v>3.1</v>
       </c>
       <c r="M284" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N284" t="n">
-        <v>5.4</v>
+        <v>2.24</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37946,10 +37946,10 @@
         <v>0</v>
       </c>
       <c r="AB284" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC284" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD284" t="n">
         <v>0</v>
@@ -37994,7 +37994,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -38004,12 +38004,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -38030,13 +38030,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -38078,10 +38078,10 @@
         <v>0</v>
       </c>
       <c r="AB285" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC285" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD285" t="n">
         <v>0</v>
@@ -38126,7 +38126,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -38136,12 +38136,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -38258,7 +38258,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -38268,12 +38268,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -38294,13 +38294,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N287" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -38342,10 +38342,10 @@
         <v>0</v>
       </c>
       <c r="AB287" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC287" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD287" t="n">
         <v>0</v>
@@ -38390,7 +38390,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -38400,12 +38400,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -38426,13 +38426,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -38474,10 +38474,10 @@
         <v>0</v>
       </c>
       <c r="AB288" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC288" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD288" t="n">
         <v>0</v>
@@ -38522,7 +38522,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -38532,12 +38532,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -38654,7 +38654,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -38664,12 +38664,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -38786,7 +38786,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -38796,12 +38796,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M291" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -38870,10 +38870,10 @@
         <v>0</v>
       </c>
       <c r="AB291" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC291" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD291" t="n">
         <v>0</v>
@@ -38918,7 +38918,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -38928,12 +38928,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38954,13 +38954,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M292" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N292" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -39002,10 +39002,10 @@
         <v>0</v>
       </c>
       <c r="AB292" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC292" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD292" t="n">
         <v>0</v>
@@ -39060,12 +39060,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -39086,13 +39086,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="M293" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N293" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -39134,16 +39134,16 @@
         <v>0</v>
       </c>
       <c r="AB293" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC293" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD293" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE293" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF293" t="n">
         <v>0</v>
@@ -39324,12 +39324,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -39350,13 +39350,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="M295" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N295" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -39398,16 +39398,16 @@
         <v>0</v>
       </c>
       <c r="AB295" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AE295" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AC295" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD295" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE295" t="n">
-        <v>0</v>
       </c>
       <c r="AF295" t="n">
         <v>0</v>
@@ -39578,7 +39578,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -39588,12 +39588,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -39842,7 +39842,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -39852,12 +39852,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G299" t="n">

--- a/jogos_2025-08-09.xlsx
+++ b/jogos_2025-08-09.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>1.59</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.74</v>
+        <v>2.49</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2525,10 +2525,10 @@
         <v>1.77</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.59</v>
+        <v>2.08</v>
       </c>
       <c r="M17" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>2.95</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>2.37</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.49</v>
+        <v>1.74</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.65</v>
+        <v>1.61</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>2.65</v>
+        <v>5.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,22 +7766,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8378,10 +8378,10 @@
         <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8642,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD62" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9434,10 +9434,10 @@
         <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9878,22 +9878,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10274,22 +10274,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10538,22 +10538,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="M83" t="n">
-        <v>3.83</v>
+        <v>3.12</v>
       </c>
       <c r="N83" t="n">
-        <v>4.33</v>
+        <v>2.77</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD83" t="n">
         <v>0</v>
@@ -11462,22 +11462,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11678,10 +11678,10 @@
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD85" t="n">
         <v>0</v>
@@ -11726,22 +11726,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11810,10 +11810,10 @@
         <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -11858,22 +11858,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11942,10 +11942,10 @@
         <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
@@ -12122,22 +12122,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12338,10 +12338,10 @@
         <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -12386,22 +12386,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12734,10 +12734,10 @@
         <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -12782,22 +12782,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13130,10 +13130,10 @@
         <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13178,22 +13178,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13478,13 +13478,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13526,10 +13526,10 @@
         <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -13574,22 +13574,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13970,22 +13970,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14102,22 +14102,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14138,13 +14138,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -14186,10 +14186,10 @@
         <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14318,10 +14318,10 @@
         <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14450,10 +14450,10 @@
         <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -15110,10 +15110,10 @@
         <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD111" t="n">
         <v>0</v>
@@ -15158,22 +15158,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15290,22 +15290,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15374,10 +15374,10 @@
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15422,7 +15422,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15506,10 +15506,10 @@
         <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15686,22 +15686,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15854,13 +15854,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15902,10 +15902,10 @@
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15986,13 +15986,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="M118" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N118" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -16034,10 +16034,10 @@
         <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC118" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -16118,13 +16118,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD119" t="n">
         <v>0</v>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -16346,22 +16346,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16742,22 +16742,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16778,13 +16778,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16826,10 +16826,10 @@
         <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
         <v>0</v>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16910,13 +16910,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16958,10 +16958,10 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD125" t="n">
         <v>0</v>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -17042,13 +17042,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17174,13 +17174,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -17222,10 +17222,10 @@
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17270,22 +17270,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17486,10 +17486,10 @@
         <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD129" t="n">
         <v>0</v>
@@ -17544,12 +17544,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17666,22 +17666,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17808,12 +17808,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -18062,22 +18062,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -18098,13 +18098,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -18146,10 +18146,10 @@
         <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD134" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18204,12 +18204,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD135" t="n">
         <v>0</v>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD136" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18494,13 +18494,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18542,10 +18542,10 @@
         <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD137" t="n">
         <v>0</v>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18600,12 +18600,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18732,12 +18732,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18758,13 +18758,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.46</v>
+        <v>2.47</v>
       </c>
       <c r="M139" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="N139" t="n">
-        <v>6.4</v>
+        <v>2.85</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18806,10 +18806,10 @@
         <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC139" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD139" t="n">
         <v>0</v>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18890,13 +18890,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18938,10 +18938,10 @@
         <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD140" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18996,12 +18996,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -19128,12 +19128,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -19260,12 +19260,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -19392,12 +19392,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19460,10 +19460,10 @@
         <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB144" t="n">
         <v>0</v>
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19550,13 +19550,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19598,10 +19598,10 @@
         <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC145" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD145" t="n">
         <v>0</v>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19920,12 +19920,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19942,17 +19942,17 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19994,10 +19994,10 @@
         <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC148" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD148" t="n">
         <v>0</v>
@@ -20042,22 +20042,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -20078,13 +20078,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -20126,10 +20126,10 @@
         <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC149" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD149" t="n">
         <v>0</v>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -20184,12 +20184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20210,13 +20210,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -20258,10 +20258,10 @@
         <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC150" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD150" t="n">
         <v>0</v>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -20316,12 +20316,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20342,13 +20342,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -20390,10 +20390,10 @@
         <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC151" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD151" t="n">
         <v>0</v>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20470,17 +20470,17 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20522,10 +20522,10 @@
         <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD152" t="n">
         <v>0</v>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20580,12 +20580,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20606,13 +20606,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20654,10 +20654,10 @@
         <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD153" t="n">
         <v>0</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20712,12 +20712,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.66</v>
+        <v>2.62</v>
       </c>
       <c r="M154" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="N154" t="n">
-        <v>5.2</v>
+        <v>2.57</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20786,10 +20786,10 @@
         <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="AC154" t="n">
-        <v>1.54</v>
+        <v>1.97</v>
       </c>
       <c r="AD154" t="n">
         <v>0</v>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20870,13 +20870,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20918,10 +20918,10 @@
         <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD155" t="n">
         <v>0</v>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20976,12 +20976,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -21002,13 +21002,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -21050,10 +21050,10 @@
         <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC156" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD156" t="n">
         <v>0</v>
@@ -21230,22 +21230,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -21314,10 +21314,10 @@
         <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -21372,12 +21372,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21578,10 +21578,10 @@
         <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21636,12 +21636,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21710,10 +21710,10 @@
         <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
         <v>0</v>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21768,12 +21768,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21842,10 +21842,10 @@
         <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC162" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD162" t="n">
         <v>0</v>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21900,12 +21900,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21926,13 +21926,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21974,10 +21974,10 @@
         <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD163" t="n">
         <v>0</v>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -22058,13 +22058,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -22100,10 +22100,10 @@
         <v>0</v>
       </c>
       <c r="Z164" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
         <v>0</v>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22296,12 +22296,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -22322,13 +22322,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -22370,10 +22370,10 @@
         <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD166" t="n">
         <v>0</v>
@@ -22418,22 +22418,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22454,13 +22454,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22560,12 +22560,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22634,10 +22634,10 @@
         <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD168" t="n">
         <v>0</v>
@@ -22682,22 +22682,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22718,13 +22718,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22956,12 +22956,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -23078,22 +23078,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -23220,12 +23220,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -23352,12 +23352,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23474,22 +23474,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23616,12 +23616,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23748,12 +23748,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -24002,7 +24002,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -24134,22 +24134,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -24266,22 +24266,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -24398,22 +24398,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24530,22 +24530,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24698,13 +24698,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24752,10 +24752,10 @@
         <v>0</v>
       </c>
       <c r="AD184" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE184" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF184" t="n">
         <v>0</v>
@@ -24794,22 +24794,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24826,17 +24826,17 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24872,10 +24872,10 @@
         <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB185" t="n">
         <v>0</v>
@@ -24926,22 +24926,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24958,17 +24958,17 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -25004,10 +25004,10 @@
         <v>0</v>
       </c>
       <c r="Z186" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB186" t="n">
         <v>0</v>
@@ -25058,22 +25058,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -25094,13 +25094,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -25142,10 +25142,10 @@
         <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC187" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD187" t="n">
         <v>0</v>
@@ -25322,22 +25322,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25358,13 +25358,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -25406,10 +25406,10 @@
         <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD189" t="n">
         <v>0</v>
@@ -25454,7 +25454,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25490,13 +25490,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="M190" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="N190" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -25538,16 +25538,16 @@
         <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC190" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD190" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AE190" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AF190" t="n">
         <v>0</v>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25596,12 +25596,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25622,13 +25622,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25670,16 +25670,16 @@
         <v>0</v>
       </c>
       <c r="AB191" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC191" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD191" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE191" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF191" t="n">
         <v>0</v>
@@ -25850,7 +25850,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25886,13 +25886,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26018,13 +26018,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -26906,7 +26906,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -27048,12 +27048,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -27074,13 +27074,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="M202" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N202" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC202" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD202" t="n">
         <v>0</v>
@@ -27170,7 +27170,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -27180,12 +27180,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27206,13 +27206,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -27254,10 +27254,10 @@
         <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD203" t="n">
         <v>0</v>
@@ -27302,22 +27302,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27434,22 +27434,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -27518,10 +27518,10 @@
         <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC205" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD205" t="n">
         <v>0</v>
@@ -27566,7 +27566,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -27576,12 +27576,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27698,22 +27698,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27840,12 +27840,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -28094,22 +28094,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28226,7 +28226,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -28236,12 +28236,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -28262,13 +28262,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -28310,10 +28310,10 @@
         <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD211" t="n">
         <v>0</v>
@@ -28358,22 +28358,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -28394,13 +28394,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -28442,10 +28442,10 @@
         <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD212" t="n">
         <v>0</v>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -28500,12 +28500,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28622,22 +28622,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28754,22 +28754,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28790,13 +28790,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28838,10 +28838,10 @@
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC215" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD215" t="n">
         <v>0</v>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -29018,22 +29018,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29054,13 +29054,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -29102,10 +29102,10 @@
         <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC217" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD217" t="n">
         <v>0</v>
@@ -29150,7 +29150,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -29160,12 +29160,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29424,12 +29424,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29678,7 +29678,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29688,12 +29688,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29714,13 +29714,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29762,10 +29762,10 @@
         <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD222" t="n">
         <v>0</v>
@@ -29810,7 +29810,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29820,12 +29820,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29942,7 +29942,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29952,12 +29952,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29978,13 +29978,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -30026,10 +30026,10 @@
         <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC224" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD224" t="n">
         <v>0</v>
@@ -30074,7 +30074,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -30084,12 +30084,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30242,13 +30242,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -30338,7 +30338,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -30348,12 +30348,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30506,13 +30506,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -30612,12 +30612,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30638,13 +30638,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -30680,10 +30680,10 @@
         <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
         <v>0</v>
@@ -30734,7 +30734,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30744,12 +30744,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30876,12 +30876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -31130,22 +31130,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -31166,13 +31166,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -31272,12 +31272,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -31298,13 +31298,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -31340,10 +31340,10 @@
         <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA234" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB234" t="n">
         <v>0</v>
@@ -31536,12 +31536,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31658,22 +31658,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31694,13 +31694,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31736,10 +31736,10 @@
         <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA237" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB237" t="n">
         <v>0</v>
@@ -31922,22 +31922,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31958,13 +31958,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -32186,22 +32186,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32222,13 +32222,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -32264,10 +32264,10 @@
         <v>0</v>
       </c>
       <c r="Z241" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA241" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB241" t="n">
         <v>0</v>
@@ -32450,22 +32450,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -32486,13 +32486,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -32534,16 +32534,16 @@
         <v>0</v>
       </c>
       <c r="AB243" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC243" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD243" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE243" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF243" t="n">
         <v>0</v>
@@ -32582,22 +32582,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -32714,22 +32714,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32750,13 +32750,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32798,16 +32798,16 @@
         <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC245" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD245" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF245" t="n">
         <v>0</v>
@@ -32846,22 +32846,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -33252,12 +33252,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33648,12 +33648,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33780,12 +33780,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -34044,12 +34044,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -34176,12 +34176,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -34430,7 +34430,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -34440,12 +34440,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -34466,13 +34466,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -34514,10 +34514,10 @@
         <v>0</v>
       </c>
       <c r="AB258" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC258" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD258" t="n">
         <v>0</v>
@@ -34572,12 +34572,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -34598,13 +34598,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="M259" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="N259" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -34649,7 +34649,7 @@
         <v>2.3</v>
       </c>
       <c r="AC259" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD259" t="n">
         <v>0</v>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -34704,12 +34704,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34730,13 +34730,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -34778,10 +34778,10 @@
         <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC260" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD260" t="n">
         <v>0</v>
@@ -34826,7 +34826,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34836,12 +34836,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34862,13 +34862,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34910,10 +34910,10 @@
         <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC261" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD261" t="n">
         <v>0</v>
@@ -34958,7 +34958,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34968,12 +34968,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34994,13 +34994,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -35042,10 +35042,10 @@
         <v>0</v>
       </c>
       <c r="AB262" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC262" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD262" t="n">
         <v>0</v>
@@ -35090,7 +35090,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -35100,12 +35100,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -35222,7 +35222,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -35232,12 +35232,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -35354,7 +35354,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -35364,12 +35364,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -35496,12 +35496,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -35628,12 +35628,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -35760,12 +35760,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35882,7 +35882,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35892,12 +35892,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -36024,12 +36024,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -36156,12 +36156,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -36278,7 +36278,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -36288,12 +36288,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -36674,7 +36674,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -36684,12 +36684,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -36816,12 +36816,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36948,12 +36948,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -37080,12 +37080,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -37212,12 +37212,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -37238,13 +37238,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="M279" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N279" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -37286,10 +37286,10 @@
         <v>0</v>
       </c>
       <c r="AB279" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC279" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD279" t="n">
         <v>0</v>
@@ -37334,7 +37334,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -37344,12 +37344,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -37370,13 +37370,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="M280" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="N280" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -37418,10 +37418,10 @@
         <v>0</v>
       </c>
       <c r="AB280" t="n">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="AC280" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AD280" t="n">
         <v>0</v>
@@ -37466,7 +37466,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -37476,12 +37476,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -37502,13 +37502,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N281" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -37550,10 +37550,10 @@
         <v>0</v>
       </c>
       <c r="AB281" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC281" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD281" t="n">
         <v>0</v>
@@ -37598,7 +37598,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -37608,12 +37608,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -37634,13 +37634,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -37682,10 +37682,10 @@
         <v>0</v>
       </c>
       <c r="AB282" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC282" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD282" t="n">
         <v>0</v>
@@ -37730,7 +37730,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -37740,12 +37740,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37766,13 +37766,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -37814,10 +37814,10 @@
         <v>0</v>
       </c>
       <c r="AB283" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC283" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD283" t="n">
         <v>0</v>
@@ -37872,12 +37872,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37898,13 +37898,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>3.1</v>
+        <v>1.56</v>
       </c>
       <c r="M284" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N284" t="n">
-        <v>2.24</v>
+        <v>5.4</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37946,10 +37946,10 @@
         <v>0</v>
       </c>
       <c r="AB284" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC284" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD284" t="n">
         <v>0</v>
@@ -37994,7 +37994,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -38004,12 +38004,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -38030,13 +38030,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -38078,10 +38078,10 @@
         <v>0</v>
       </c>
       <c r="AB285" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC285" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD285" t="n">
         <v>0</v>
@@ -38126,7 +38126,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -38136,12 +38136,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -38258,7 +38258,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -38268,12 +38268,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -38390,7 +38390,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -38400,12 +38400,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -38426,13 +38426,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N288" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -38474,10 +38474,10 @@
         <v>0</v>
       </c>
       <c r="AB288" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC288" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD288" t="n">
         <v>0</v>
@@ -38522,7 +38522,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -38532,12 +38532,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -38654,7 +38654,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -38664,12 +38664,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -38690,13 +38690,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M290" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -38738,10 +38738,10 @@
         <v>0</v>
       </c>
       <c r="AB290" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC290" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD290" t="n">
         <v>0</v>
@@ -38786,7 +38786,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -38796,12 +38796,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N291" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -38870,10 +38870,10 @@
         <v>0</v>
       </c>
       <c r="AB291" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC291" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD291" t="n">
         <v>0</v>
@@ -38918,7 +38918,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -38928,12 +38928,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38954,13 +38954,13 @@
         </is>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M292" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -39002,10 +39002,10 @@
         <v>0</v>
       </c>
       <c r="AB292" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC292" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD292" t="n">
         <v>0</v>
@@ -39060,12 +39060,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -39086,13 +39086,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="M293" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N293" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -39134,10 +39134,10 @@
         <v>0</v>
       </c>
       <c r="AB293" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AC293" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AD293" t="n">
         <v>0</v>
@@ -39192,12 +39192,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -39218,58 +39218,58 @@
         </is>
       </c>
       <c r="L294" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M294" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N294" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>0</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="n">
+        <v>0</v>
+      </c>
+      <c r="T294" t="n">
+        <v>0</v>
+      </c>
+      <c r="U294" t="n">
+        <v>0</v>
+      </c>
+      <c r="V294" t="n">
+        <v>0</v>
+      </c>
+      <c r="W294" t="n">
+        <v>0</v>
+      </c>
+      <c r="X294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB294" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC294" t="n">
         <v>2.1</v>
-      </c>
-      <c r="M294" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N294" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O294" t="n">
-        <v>0</v>
-      </c>
-      <c r="P294" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
-      <c r="R294" t="n">
-        <v>0</v>
-      </c>
-      <c r="S294" t="n">
-        <v>0</v>
-      </c>
-      <c r="T294" t="n">
-        <v>0</v>
-      </c>
-      <c r="U294" t="n">
-        <v>0</v>
-      </c>
-      <c r="V294" t="n">
-        <v>0</v>
-      </c>
-      <c r="W294" t="n">
-        <v>0</v>
-      </c>
-      <c r="X294" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y294" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB294" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC294" t="n">
-        <v>1.67</v>
       </c>
       <c r="AD294" t="n">
         <v>0</v>
@@ -39578,7 +39578,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -39588,12 +39588,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -39842,7 +39842,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -39852,12 +39852,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39974,7 +39974,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -39984,12 +39984,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -40010,13 +40010,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N300" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -40058,10 +40058,10 @@
         <v>0</v>
       </c>
       <c r="AB300" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC300" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD300" t="n">
         <v>0</v>
@@ -40106,7 +40106,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -40116,12 +40116,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -40142,13 +40142,13 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M301" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N301" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -40190,10 +40190,10 @@
         <v>0</v>
       </c>
       <c r="AB301" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC301" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD301" t="n">
         <v>0</v>

--- a/jogos_2025-08-09.xlsx
+++ b/jogos_2025-08-09.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="M6" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="M7" t="n">
-        <v>3.26</v>
+        <v>3.74</v>
       </c>
       <c r="N7" t="n">
-        <v>2.74</v>
+        <v>3.71</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.01</v>
+        <v>3.14</v>
       </c>
       <c r="N8" t="n">
-        <v>2.69</v>
+        <v>2.32</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="M10" t="n">
-        <v>3.32</v>
+        <v>2.91</v>
       </c>
       <c r="N10" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="M11" t="n">
-        <v>3.84</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>3.47</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>2.09</v>
       </c>
       <c r="M12" t="n">
-        <v>4.6</v>
+        <v>3.31</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.49</v>
+        <v>3.63</v>
       </c>
       <c r="M13" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>1.89</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.42</v>
+        <v>1.82</v>
       </c>
       <c r="M15" t="n">
-        <v>3.13</v>
+        <v>3.32</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>3.74</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.09</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
-        <v>3.31</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.95</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.47</v>
+        <v>3.99</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.72</v>
+        <v>2.49</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="N18" t="n">
-        <v>3.99</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.04</v>
+        <v>2.42</v>
       </c>
       <c r="M19" t="n">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>1.73</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.85</v>
+        <v>1.73</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4730,22 +4730,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,58 +5030,58 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.73</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="N35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.87</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.44</v>
+        <v>1.7</v>
       </c>
       <c r="M36" t="n">
-        <v>3.23</v>
+        <v>3.76</v>
       </c>
       <c r="N36" t="n">
-        <v>2.86</v>
+        <v>4.7</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="M37" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="N37" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5918,22 +5918,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6446,22 +6446,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,22 +6578,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6710,22 +6710,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="M48" t="n">
-        <v>2.95</v>
+        <v>3.52</v>
       </c>
       <c r="N48" t="n">
-        <v>4.2</v>
+        <v>4.73</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6842,22 +6842,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7190,10 +7190,10 @@
         <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7238,22 +7238,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7274,13 +7274,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.65</v>
+        <v>1.61</v>
       </c>
       <c r="M52" t="n">
         <v>3.55</v>
       </c>
       <c r="N52" t="n">
-        <v>2.35</v>
+        <v>4.6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7322,10 +7322,10 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7370,22 +7370,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7406,13 +7406,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7454,10 +7454,10 @@
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7512,12 +7512,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="M56" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="N56" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7850,10 +7850,10 @@
         <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -7898,22 +7898,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7934,13 +7934,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8462,13 +8462,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8510,10 +8510,10 @@
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8726,13 +8726,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8774,10 +8774,10 @@
         <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8858,13 +8858,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8906,10 +8906,10 @@
         <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9482,22 +9482,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9518,13 +9518,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9566,10 +9566,10 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10142,22 +10142,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10178,13 +10178,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10226,10 +10226,10 @@
         <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Turan Turkistan</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10358,10 +10358,10 @@
         <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10442,13 +10442,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10574,13 +10574,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10706,13 +10706,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10754,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
         <v>0</v>
@@ -10802,22 +10802,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10838,13 +10838,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10886,10 +10886,10 @@
         <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Turan Turkistan</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
         <v>0</v>
@@ -11066,22 +11066,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12422,13 +12422,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="M91" t="n">
         <v>3.45</v>
       </c>
       <c r="N91" t="n">
-        <v>3.69</v>
+        <v>4.6</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12470,10 +12470,10 @@
         <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12950,13 +12950,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="M95" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="N95" t="n">
-        <v>3.39</v>
+        <v>2.75</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12998,10 +12998,10 @@
         <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13716,12 +13716,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="N101" t="n">
-        <v>4.6</v>
+        <v>3.39</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -15564,12 +15564,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15590,13 +15590,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="M115" t="n">
-        <v>3.11</v>
+        <v>3.45</v>
       </c>
       <c r="N115" t="n">
-        <v>3.01</v>
+        <v>3.69</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15638,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -15696,12 +15696,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="M116" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="N116" t="n">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15770,7 +15770,7 @@
         <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC116" t="n">
         <v>1.7</v>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25728,12 +25728,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25754,13 +25754,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25802,10 +25802,10 @@
         <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC192" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD192" t="n">
         <v>0</v>
@@ -25982,7 +25982,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25992,12 +25992,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26018,13 +26018,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -26066,10 +26066,10 @@
         <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC194" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD194" t="n">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26546,13 +26546,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -26594,10 +26594,10 @@
         <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD198" t="n">
         <v>0</v>
@@ -26906,22 +26906,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26942,13 +26942,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD201" t="n">
         <v>0</v>
@@ -27170,22 +27170,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -27206,13 +27206,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -27254,10 +27254,10 @@
         <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD203" t="n">
         <v>0</v>
@@ -27302,22 +27302,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -27444,12 +27444,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -27566,22 +27566,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27962,7 +27962,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -28046,10 +28046,10 @@
         <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC209" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD209" t="n">
         <v>0</v>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -28130,13 +28130,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.85</v>
+        <v>2.48</v>
       </c>
       <c r="M210" t="n">
-        <v>3.32</v>
+        <v>3.53</v>
       </c>
       <c r="N210" t="n">
-        <v>3.61</v>
+        <v>2.3</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -28178,10 +28178,10 @@
         <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC210" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD210" t="n">
         <v>0</v>
@@ -28754,7 +28754,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28764,12 +28764,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28790,13 +28790,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28838,10 +28838,10 @@
         <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC215" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD215" t="n">
         <v>0</v>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28896,12 +28896,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28922,13 +28922,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -29018,22 +29018,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -29150,22 +29150,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -29292,12 +29292,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29318,13 +29318,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>3.07</v>
+        <v>2.07</v>
       </c>
       <c r="M219" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="N219" t="n">
-        <v>2.18</v>
+        <v>3.13</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -29366,10 +29366,10 @@
         <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AC219" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AD219" t="n">
         <v>0</v>
@@ -30074,22 +30074,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30216,12 +30216,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -30470,22 +30470,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30876,12 +30876,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -32054,22 +32054,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -32090,13 +32090,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>1.69</v>
+        <v>1.19</v>
       </c>
       <c r="M240" t="n">
-        <v>3.34</v>
+        <v>7.1</v>
       </c>
       <c r="N240" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -32138,16 +32138,16 @@
         <v>0</v>
       </c>
       <c r="AB240" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD240" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC240" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD240" t="n">
-        <v>0</v>
-      </c>
       <c r="AE240" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF240" t="n">
         <v>0</v>
@@ -32186,7 +32186,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -32196,12 +32196,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -32222,13 +32222,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -32270,10 +32270,10 @@
         <v>0</v>
       </c>
       <c r="AB241" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC241" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD241" t="n">
         <v>0</v>
@@ -32318,22 +32318,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -32354,13 +32354,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -32402,16 +32402,16 @@
         <v>0</v>
       </c>
       <c r="AB242" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC242" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD242" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF242" t="n">
         <v>0</v>
@@ -32856,12 +32856,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32988,12 +32988,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -33252,12 +33252,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -33648,12 +33648,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -34044,12 +34044,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -34070,13 +34070,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -34118,10 +34118,10 @@
         <v>0</v>
       </c>
       <c r="AB255" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC255" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD255" t="n">
         <v>0</v>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -34176,12 +34176,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -34202,13 +34202,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -34250,10 +34250,10 @@
         <v>0</v>
       </c>
       <c r="AB256" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC256" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD256" t="n">
         <v>0</v>
@@ -35496,12 +35496,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -35760,12 +35760,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35882,7 +35882,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35892,12 +35892,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -36014,7 +36014,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -36024,12 +36024,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -37202,7 +37202,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -37212,12 +37212,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -37238,13 +37238,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -37286,10 +37286,10 @@
         <v>0</v>
       </c>
       <c r="AB279" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC279" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD279" t="n">
         <v>0</v>
@@ -37334,7 +37334,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -37344,12 +37344,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -37370,13 +37370,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -37418,10 +37418,10 @@
         <v>0</v>
       </c>
       <c r="AB280" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC280" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD280" t="n">
         <v>0</v>
